--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:46:32+00:00</t>
+    <t>2024-11-16T15:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T15:52:33+00:00</t>
+    <t>2024-11-16T16:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
+++ b/r5-core-27-IndexPage-Update/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-16T16:02:40+00:00</t>
+    <t>2025-01-17T11:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1228,30 +1228,29 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.
-The ISO21090-codedString may be used to provide a coded representation of the contents of strings in an Address.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R5/location.html#) resource).</t>
+    <t>Address(es) of the practitioner that are not role specific (typically home address)</t>
+  </si>
+  <si>
+    <t>Address(es) of the practitioner that are not role specific (typically home address). +Work addresses are not typically entered in this property as they are usually role dependent.</t>
+  </si>
+  <si>
+    <t>The PractitionerRole does not have an address value on it, as it is expected that the location property be used for this purpose (which has an address).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
-  </si>
-  <si>
-    <t>XAD</t>
-  </si>
-  <si>
-    <t>n/a,AD</t>
-  </si>
-  <si>
-    <t>Address</t>
+    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
+  </si>
+  <si>
+    <t>./addr</t>
+  </si>
+  <si>
+    <t>ParticipantContactable.address</t>
+  </si>
+  <si>
+    <t>./Addresses</t>
   </si>
   <si>
     <t>Practitioner.photo</t>
@@ -1808,7 +1807,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.37109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.08984375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="142.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.98046875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="52.3828125" customWidth="true" bestFit="true"/>
@@ -5816,7 +5815,7 @@
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -10507,7 +10506,7 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>387</v>
@@ -10583,19 +10582,19 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL75" t="s" s="2">
+      <c r="AM75" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>395</v>
